--- a/exports/trend_1d/CDSL_full_report.xlsx
+++ b/exports/trend_1d/CDSL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>14.38</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42944</v>
+        <v>42947</v>
       </c>
       <c r="H2" t="n">
-        <v>186.8</v>
+        <v>169.8</v>
       </c>
       <c r="I2" t="n">
         <v>171.19</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.58</v>
+        <v>-15.08</v>
       </c>
       <c r="L2" t="n">
         <v>15.6</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>27.03</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42996</v>
+        <v>42997</v>
       </c>
       <c r="H3" t="n">
-        <v>180.8</v>
+        <v>185.3</v>
       </c>
       <c r="I3" t="n">
         <v>182.0320963388259</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.48</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>8.949999999999999</v>
+        <v>11.48</v>
       </c>
       <c r="M3" t="n">
         <v>2.43</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.65</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H4" t="n">
-        <v>176.6</v>
+        <v>170.5</v>
       </c>
       <c r="I4" t="n">
         <v>171.0012512682928</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.7</v>
+        <v>-7.99</v>
       </c>
       <c r="L4" t="n">
-        <v>7.12</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M4" t="n">
         <v>0.6</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.4</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43024</v>
+        <v>43025</v>
       </c>
       <c r="H5" t="n">
-        <v>191.9</v>
+        <v>195</v>
       </c>
       <c r="I5" t="n">
         <v>192.7758892247272</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>-12.55</v>
+        <v>-14.37</v>
       </c>
       <c r="L5" t="n">
-        <v>15.31</v>
+        <v>15.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.23</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>11.42</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43073</v>
+        <v>43074</v>
       </c>
       <c r="H6" t="n">
-        <v>176.25</v>
+        <v>174.45</v>
       </c>
       <c r="I6" t="n">
         <v>175.0773868254036</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.619999999999999</v>
+        <v>-10.54</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>11.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.83</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43087</v>
+        <v>43088</v>
       </c>
       <c r="H7" t="n">
-        <v>174.6</v>
+        <v>180.6</v>
       </c>
       <c r="I7" t="n">
         <v>180.4895109359322</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09</v>
+        <v>-3.53</v>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>5.19</v>
       </c>
       <c r="M7" t="n">
         <v>0.62</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43125</v>
+        <v>43129</v>
       </c>
       <c r="H8" t="n">
-        <v>174.15</v>
+        <v>169.85</v>
       </c>
       <c r="I8" t="n">
         <v>170.1313947733937</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.57</v>
+        <v>-5.95</v>
       </c>
       <c r="L8" t="n">
-        <v>3.93</v>
+        <v>6.28</v>
       </c>
       <c r="M8" t="n">
         <v>0.17</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.12</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43194</v>
+        <v>43195</v>
       </c>
       <c r="H9" t="n">
-        <v>148.6</v>
+        <v>154.2</v>
       </c>
       <c r="I9" t="n">
         <v>153.3873594945019</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K9" t="n">
-        <v>12.51</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>3.56</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>11.51</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H10" t="n">
-        <v>142.9</v>
+        <v>136.35</v>
       </c>
       <c r="I10" t="n">
         <v>137.5864432445942</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.33</v>
+        <v>-11.58</v>
       </c>
       <c r="L10" t="n">
-        <v>12.06</v>
+        <v>12.13</v>
       </c>
       <c r="M10" t="n">
         <v>0.87</v>
       </c>
       <c r="N10" t="n">
-        <v>2.52</v>
+        <v>4.58</v>
       </c>
       <c r="O10" t="n">
         <v>3.77</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>11.12</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43249</v>
+        <v>43250</v>
       </c>
       <c r="H11" t="n">
-        <v>135.5</v>
+        <v>147.2</v>
       </c>
       <c r="I11" t="n">
         <v>144.5993243990223</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>0.62</v>
+        <v>-7.96</v>
       </c>
       <c r="L11" t="n">
-        <v>5.17</v>
+        <v>10.6</v>
       </c>
       <c r="M11" t="n">
         <v>0.68</v>
       </c>
       <c r="N11" t="n">
-        <v>2.17</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-4.58</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>13.28</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H12" t="n">
-        <v>133.7</v>
+        <v>131.1</v>
       </c>
       <c r="I12" t="n">
         <v>132.9882798599633</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.17</v>
+        <v>-10.94</v>
       </c>
       <c r="L12" t="n">
-        <v>10.9</v>
+        <v>11.35</v>
       </c>
       <c r="M12" t="n">
         <v>0.95</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43405</v>
+        <v>43406</v>
       </c>
       <c r="H13" t="n">
-        <v>120.5</v>
+        <v>122.35</v>
       </c>
       <c r="I13" t="n">
         <v>122.0804451212197</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K13" t="n">
-        <v>8.09</v>
+        <v>6.67</v>
       </c>
       <c r="L13" t="n">
         <v>6.29</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43440</v>
+        <v>43441</v>
       </c>
       <c r="H14" t="n">
-        <v>113.8</v>
+        <v>111.2</v>
       </c>
       <c r="I14" t="n">
         <v>113.6450922807528</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.99</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>7.64</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>1.67</v>
       </c>
       <c r="N14" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="O14" t="n">
         <v>1.54</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.57</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H15" t="n">
-        <v>110.25</v>
+        <v>114.6</v>
       </c>
       <c r="I15" t="n">
         <v>111.600288402405</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K15" t="n">
-        <v>0.85</v>
+        <v>-3.06</v>
       </c>
       <c r="L15" t="n">
         <v>7.42</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.81</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43606</v>
+        <v>43607</v>
       </c>
       <c r="H16" t="n">
-        <v>111.7</v>
+        <v>111.25</v>
       </c>
       <c r="I16" t="n">
         <v>111.4701637417344</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.53</v>
+        <v>-2.92</v>
       </c>
       <c r="L16" t="n">
         <v>4.01</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.81</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H17" t="n">
-        <v>99.45</v>
+        <v>103.75</v>
       </c>
       <c r="I17" t="n">
         <v>99.78192163597474</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K17" t="n">
-        <v>10.61</v>
+        <v>6.74</v>
       </c>
       <c r="L17" t="n">
         <v>5.84</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H18" t="n">
-        <v>132.5</v>
+        <v>126.5</v>
       </c>
       <c r="I18" t="n">
         <v>129.1211197457336</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K18" t="n">
-        <v>27.71</v>
+        <v>21.93</v>
       </c>
       <c r="L18" t="n">
         <v>6.31</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>19.79</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43970</v>
+        <v>43971</v>
       </c>
       <c r="H19" t="n">
-        <v>112.45</v>
+        <v>121.3</v>
       </c>
       <c r="I19" t="n">
         <v>121.2115959736248</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K19" t="n">
-        <v>11.11</v>
+        <v>4.11</v>
       </c>
       <c r="L19" t="n">
         <v>8.300000000000001</v>
@@ -1524,7 +1751,7 @@
         <v>3.39</v>
       </c>
       <c r="N19" t="n">
-        <v>7.08</v>
+        <v>7.87</v>
       </c>
       <c r="O19" t="n">
         <v>-4.53</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>15.3</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H20" t="n">
-        <v>252.7</v>
+        <v>243.95</v>
       </c>
       <c r="I20" t="n">
         <v>245.3935547641827</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K20" t="n">
-        <v>108.33</v>
+        <v>101.11</v>
       </c>
       <c r="L20" t="n">
         <v>7.09</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>12.26</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44238</v>
+        <v>44239</v>
       </c>
       <c r="H21" t="n">
-        <v>259.2</v>
+        <v>269</v>
       </c>
       <c r="I21" t="n">
         <v>265.8887625652405</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.25</v>
+        <v>-10.27</v>
       </c>
       <c r="L21" t="n">
-        <v>9.859999999999999</v>
+        <v>10.68</v>
       </c>
       <c r="M21" t="n">
         <v>4.15</v>
       </c>
       <c r="N21" t="n">
-        <v>3.34</v>
+        <v>3.78</v>
       </c>
       <c r="O21" t="n">
         <v>-3.46</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.91</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44418</v>
+        <v>44419</v>
       </c>
       <c r="H22" t="n">
-        <v>640.2</v>
+        <v>630.3</v>
       </c>
       <c r="I22" t="n">
         <v>638.4171522036701</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K22" t="n">
-        <v>137.99</v>
+        <v>134.31</v>
       </c>
       <c r="L22" t="n">
         <v>3.88</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>16.93</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44448</v>
+        <v>44452</v>
       </c>
       <c r="H23" t="n">
-        <v>660.7</v>
+        <v>689</v>
       </c>
       <c r="I23" t="n">
         <v>668.7284552162371</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.82</v>
+        <v>-9.31</v>
       </c>
       <c r="L23" t="n">
-        <v>4.82</v>
+        <v>9.31</v>
       </c>
       <c r="M23" t="n">
         <v>2.8</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>12.32</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44526</v>
+        <v>44529</v>
       </c>
       <c r="H24" t="n">
-        <v>707.3</v>
+        <v>685.1</v>
       </c>
       <c r="I24" t="n">
         <v>693.4363216780836</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K24" t="n">
-        <v>2.66</v>
+        <v>-0.57</v>
       </c>
       <c r="L24" t="n">
         <v>9.289999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="N24" t="n">
         <v>4.66</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>13.48</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44540</v>
+        <v>44543</v>
       </c>
       <c r="H25" t="n">
-        <v>764.7</v>
+        <v>793.1</v>
       </c>
       <c r="I25" t="n">
         <v>777.4191288965656</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-11.62</v>
+        <v>-15.76</v>
       </c>
       <c r="L25" t="n">
-        <v>16.33</v>
+        <v>20.05</v>
       </c>
       <c r="M25" t="n">
         <v>2.26</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.61</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H26" t="n">
-        <v>759.8</v>
+        <v>729.95</v>
       </c>
       <c r="I26" t="n">
         <v>742.9993751410987</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.2</v>
+        <v>-7.96</v>
       </c>
       <c r="L26" t="n">
         <v>9.76</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>11.52</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H27" t="n">
-        <v>733.3</v>
+        <v>759.45</v>
       </c>
       <c r="I27" t="n">
         <v>741.8652310498771</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.46</v>
+        <v>-4.04</v>
       </c>
       <c r="L27" t="n">
-        <v>3.77</v>
+        <v>7.54</v>
       </c>
       <c r="M27" t="n">
         <v>4.22</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>12.99</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H28" t="n">
-        <v>703.6</v>
+        <v>696.5</v>
       </c>
       <c r="I28" t="n">
         <v>697.7290939165265</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.35</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>8.42</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>0.84</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>7.82</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H29" t="n">
-        <v>561.5</v>
+        <v>628.7</v>
       </c>
       <c r="I29" t="n">
         <v>593.467118293065</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K29" t="n">
-        <v>19.38</v>
+        <v>9.73</v>
       </c>
       <c r="L29" t="n">
         <v>3.27</v>
@@ -2094,7 +2441,7 @@
         <v>3.03</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>11.97</v>
       </c>
       <c r="O29" t="n">
         <v>-1.01</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>18.01</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H30" t="n">
-        <v>652.7</v>
+        <v>626.7</v>
       </c>
       <c r="I30" t="n">
         <v>638.0583541401325</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K30" t="n">
-        <v>3.82</v>
+        <v>-0.32</v>
       </c>
       <c r="L30" t="n">
         <v>15.16</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>11.37</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H31" t="n">
-        <v>475.7</v>
+        <v>486.9</v>
       </c>
       <c r="I31" t="n">
         <v>485.1536879222756</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K31" t="n">
-        <v>24.09</v>
+        <v>22.31</v>
       </c>
       <c r="L31" t="n">
         <v>3.59</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>8</v>
+      </c>
+      <c r="U31" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.67</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="H32" t="n">
-        <v>581.1</v>
+        <v>579.4</v>
       </c>
       <c r="I32" t="n">
         <v>580.4339333435981</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K32" t="n">
-        <v>19.35</v>
+        <v>19</v>
       </c>
       <c r="L32" t="n">
         <v>2.22</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>8.02</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45173</v>
+        <v>45174</v>
       </c>
       <c r="H33" t="n">
-        <v>575.8</v>
+        <v>612.7</v>
       </c>
       <c r="I33" t="n">
         <v>603.284291878399</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>0.62</v>
+        <v>-5.75</v>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>6.27</v>
       </c>
       <c r="M33" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>6.41</v>
       </c>
       <c r="O33" t="n">
         <v>-0.29</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.02</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H34" t="n">
-        <v>902.3</v>
+        <v>866.7</v>
       </c>
       <c r="I34" t="n">
         <v>883.0313076480043</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K34" t="n">
-        <v>47.27</v>
+        <v>41.46</v>
       </c>
       <c r="L34" t="n">
         <v>5.7</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.32</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45328</v>
+        <v>45329</v>
       </c>
       <c r="H35" t="n">
-        <v>925.2</v>
+        <v>979</v>
       </c>
       <c r="I35" t="n">
         <v>952.1111931291733</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.75</v>
+        <v>-12.96</v>
       </c>
       <c r="L35" t="n">
-        <v>10.3</v>
+        <v>15.31</v>
       </c>
       <c r="M35" t="n">
         <v>1.26</v>
       </c>
       <c r="N35" t="n">
-        <v>3.47</v>
+        <v>5.81</v>
       </c>
       <c r="O35" t="n">
         <v>-3.95</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>12.25</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H36" t="n">
-        <v>903.7</v>
+        <v>842.3</v>
       </c>
       <c r="I36" t="n">
         <v>879.604895081015</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.69</v>
+        <v>-13.96</v>
       </c>
       <c r="L36" t="n">
-        <v>9.289999999999999</v>
+        <v>14.93</v>
       </c>
       <c r="M36" t="n">
         <v>1.99</v>
       </c>
       <c r="N36" t="n">
-        <v>4.99</v>
+        <v>6.79</v>
       </c>
       <c r="O36" t="n">
         <v>5.81</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>15.11</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="H37" t="n">
-        <v>918.85</v>
+        <v>938.1</v>
       </c>
       <c r="I37" t="n">
         <v>920.6147082286967</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.09</v>
+        <v>-11.37</v>
       </c>
       <c r="L37" t="n">
-        <v>9.52</v>
+        <v>12.15</v>
       </c>
       <c r="M37" t="n">
         <v>1.41</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.21</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H38" t="n">
-        <v>1372.6</v>
+        <v>1354.45</v>
       </c>
       <c r="I38" t="n">
         <v>1358.52417168533</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K38" t="n">
-        <v>46.32</v>
+        <v>44.38</v>
       </c>
       <c r="L38" t="n">
         <v>3.58</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.05</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45554</v>
+        <v>45555</v>
       </c>
       <c r="H39" t="n">
-        <v>1511.1</v>
+        <v>1538.65</v>
       </c>
       <c r="I39" t="n">
         <v>1512.442034669207</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-11.57</v>
+        <v>-13.6</v>
       </c>
       <c r="L39" t="n">
-        <v>15.79</v>
+        <v>16.73</v>
       </c>
       <c r="M39" t="n">
         <v>1.39</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>10.46</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H40" t="n">
-        <v>1415.3</v>
+        <v>1373.8</v>
       </c>
       <c r="I40" t="n">
         <v>1377.761858593026</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.02</v>
+        <v>-10.71</v>
       </c>
       <c r="L40" t="n">
-        <v>9.08</v>
+        <v>11.21</v>
       </c>
       <c r="M40" t="n">
         <v>1.36</v>
       </c>
       <c r="N40" t="n">
-        <v>1.83</v>
+        <v>2.93</v>
       </c>
       <c r="O40" t="n">
         <v>1.82</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.71</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45576</v>
+        <v>45579</v>
       </c>
       <c r="H41" t="n">
-        <v>1478.05</v>
+        <v>1579.3</v>
       </c>
       <c r="I41" t="n">
         <v>1514.897305706351</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.59</v>
+        <v>-14.96</v>
       </c>
       <c r="L41" t="n">
-        <v>10.28</v>
+        <v>17.56</v>
       </c>
       <c r="M41" t="n">
         <v>1.46</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.21</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H42" t="n">
-        <v>1521.9</v>
+        <v>1435.25</v>
       </c>
       <c r="I42" t="n">
         <v>1435.512645417349</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.63</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>12.54</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>16.7</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H43" t="n">
-        <v>1663.9</v>
+        <v>1718.6</v>
       </c>
       <c r="I43" t="n">
         <v>1668.500820841678</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" t="n">
-        <v>-15.93</v>
+        <v>-19.74</v>
       </c>
       <c r="L43" t="n">
-        <v>17.89</v>
+        <v>20.62</v>
       </c>
       <c r="M43" t="n">
         <v>1.28</v>
       </c>
       <c r="N43" t="n">
-        <v>2.61</v>
+        <v>3.29</v>
       </c>
       <c r="O43" t="n">
         <v>-5.69</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="H44" t="n">
-        <v>1806.65</v>
+        <v>1777.55</v>
       </c>
       <c r="I44" t="n">
         <v>1805.315916255762</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>5.12</v>
+        <v>3.43</v>
       </c>
       <c r="L44" t="n">
         <v>3.1</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H45" t="n">
-        <v>1170.3</v>
+        <v>1216.3</v>
       </c>
       <c r="I45" t="n">
         <v>1195.341391892457</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K45" t="n">
-        <v>34.16</v>
+        <v>31.57</v>
       </c>
       <c r="L45" t="n">
         <v>3.51</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.83</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H46" t="n">
-        <v>1679.3</v>
+        <v>1614.7</v>
       </c>
       <c r="I46" t="n">
         <v>1636.932522476618</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K46" t="n">
-        <v>38.07</v>
+        <v>32.76</v>
       </c>
       <c r="L46" t="n">
         <v>11.21</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.22</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H47" t="n">
-        <v>1549.4</v>
+        <v>1568.9</v>
       </c>
       <c r="I47" t="n">
         <v>1561.394692877425</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K47" t="n">
-        <v>4.04</v>
+        <v>2.84</v>
       </c>
       <c r="L47" t="n">
         <v>3.51</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.54</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H48" t="n">
-        <v>1494.8</v>
+        <v>1467.7</v>
       </c>
       <c r="I48" t="n">
         <v>1492.742724967069</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.72</v>
+        <v>-6.45</v>
       </c>
       <c r="L48" t="n">
-        <v>5.03</v>
+        <v>6.94</v>
       </c>
       <c r="M48" t="n">
         <v>0.48</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="H49" t="n">
-        <v>1558.6</v>
+        <v>1605.3</v>
       </c>
       <c r="I49" t="n">
         <v>1565.733693977628</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.19</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>8.470000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="M49" t="n">
         <v>0.36</v>
       </c>
       <c r="N49" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>-1.81</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H50" t="n">
-        <v>1550.6</v>
+        <v>1520.9</v>
       </c>
       <c r="I50" t="n">
         <v>1530.032698907002</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K50" t="n">
-        <v>-3.41</v>
+        <v>-5.26</v>
       </c>
       <c r="L50" t="n">
-        <v>6.06</v>
+        <v>6.25</v>
       </c>
       <c r="M50" t="n">
         <v>0.6</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>8.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H51" t="n">
-        <v>1331.4</v>
+        <v>1374.3</v>
       </c>
       <c r="I51" t="n">
         <v>1366.551868931643</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K51" t="n">
-        <v>12.46</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L51" t="n">
         <v>2.96</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>12.19</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H52" t="n">
-        <v>1272.2</v>
+        <v>1228.3</v>
       </c>
       <c r="I52" t="n">
         <v>1255.658701990789</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.43</v>
+        <v>-10.62</v>
       </c>
       <c r="L52" t="n">
-        <v>7.73</v>
+        <v>12.3</v>
       </c>
       <c r="M52" t="n">
-        <v>2.64</v>
+        <v>5.27</v>
       </c>
       <c r="N52" t="n">
-        <v>2.61</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>3.22</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>9.65</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H53" t="n">
-        <v>1203.5</v>
+        <v>1287.4</v>
       </c>
       <c r="I53" t="n">
         <v>1267.805427757794</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K53" t="n">
-        <v>2.02</v>
+        <v>-4.81</v>
       </c>
       <c r="L53" t="n">
-        <v>2.72</v>
+        <v>5.19</v>
       </c>
       <c r="M53" t="n">
-        <v>3.49</v>
+        <v>5.38</v>
       </c>
       <c r="N53" t="n">
-        <v>5.66</v>
+        <v>6.97</v>
       </c>
       <c r="O53" t="n">
         <v>-3.45</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>12.81</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="H54" t="n">
-        <v>1272</v>
+        <v>1238.3</v>
       </c>
       <c r="I54" t="n">
         <v>1250.528658312163</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.2</v>
+        <v>-3.81</v>
       </c>
       <c r="L54" t="n">
-        <v>2.94</v>
+        <v>4.76</v>
       </c>
       <c r="M54" t="n">
         <v>2.92</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H55" t="n">
-        <v>1264</v>
+        <v>1290.9</v>
       </c>
       <c r="I55" t="n">
         <v>1273.282855543043</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.08</v>
+        <v>-4.25</v>
       </c>
       <c r="L55" t="n">
-        <v>4.26</v>
+        <v>4.5</v>
       </c>
       <c r="M55" t="n">
         <v>1.96</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.88</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H56" t="n">
-        <v>1339.7</v>
+        <v>1323.4</v>
       </c>
       <c r="I56" t="n">
         <v>1325.365116689843</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n">
-        <v>3.78</v>
+        <v>2.52</v>
       </c>
       <c r="L56" t="n">
         <v>2.15</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.81</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="H57" t="n">
-        <v>1394.8</v>
+        <v>1434</v>
       </c>
       <c r="I57" t="n">
         <v>1411.747167878878</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.4</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>6.73</v>
+        <v>9.17</v>
       </c>
       <c r="M57" t="n">
         <v>0.9</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.47</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H58" t="n">
-        <v>1360</v>
+        <v>1311</v>
       </c>
       <c r="I58" t="n">
         <v>1329.383118355281</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.16</v>
+        <v>-8.58</v>
       </c>
       <c r="L58" t="n">
-        <v>8.26</v>
+        <v>9.17</v>
       </c>
       <c r="M58" t="n">
         <v>0.93</v>
       </c>
       <c r="N58" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="O58" t="n">
         <v>2.81</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>30</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7779,7 +8494,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="6">
@@ -7789,7 +8504,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -7799,7 +8514,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8">
@@ -7809,7 +8524,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -7819,7 +8534,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -7829,7 +8544,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>135.8</v>
       </c>
     </row>
     <row r="11">
@@ -7839,7 +8554,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -7849,7 +8564,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -7859,7 +8574,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="14">
@@ -7869,7 +8584,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.51</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="15">
@@ -7879,7 +8594,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.62</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="16">
@@ -7889,7 +8604,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="17">
@@ -7899,7 +8614,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>137.99</v>
+        <v>134.31</v>
       </c>
     </row>
     <row r="18">
@@ -7909,7 +8624,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.1</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="19">
@@ -7919,7 +8634,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -7929,7 +8644,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.09</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -7939,7 +8654,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.89</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="22">
@@ -7949,7 +8664,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -7959,7 +8674,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -7969,7 +8684,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="25">
@@ -7989,7 +8704,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.72</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="27">
@@ -7999,7 +8714,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.99</v>
+        <v>11.97</v>
       </c>
     </row>
     <row r="28">
@@ -8009,7 +8724,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
